--- a/output/coefficients/standardized/standardized_OTHER.xlsx
+++ b/output/coefficients/standardized/standardized_OTHER.xlsx
@@ -460,15 +460,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09876958677948304</v>
+        <v>0.0988</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003476687483970993</v>
+        <v>0.0035</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>28.40910701202015</v>
+        <v>28.4091</v>
       </c>
       <c r="G2" t="n">
         <v>1.56071571869917e-177</v>
@@ -481,19 +481,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02585194293462881</v>
+        <v>0.0259</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001625507782373451</v>
+        <v>0.0016</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2115450765187038</v>
+        <v>0.2115</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01330144388270822</v>
+        <v>0.0133</v>
       </c>
       <c r="F3" t="n">
-        <v>15.90391828015836</v>
+        <v>15.9039</v>
       </c>
       <c r="G3" t="n">
         <v>5.952253279975866e-57</v>
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.05370715533004308</v>
+        <v>-0.0537</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002410693064033643</v>
+        <v>0.0024</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2596277166110388</v>
+        <v>-0.2596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01165361918386716</v>
+        <v>0.0117</v>
       </c>
       <c r="F4" t="n">
-        <v>-22.27871981353722</v>
+        <v>-22.2787</v>
       </c>
       <c r="G4" t="n">
         <v>5.943237171671356e-110</v>
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001789982428150638</v>
+        <v>0.0018</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001721155220829719</v>
+        <v>0.0002</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0909008169992838</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008740555957169296</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>10.39988960024035</v>
+        <v>10.3999</v>
       </c>
       <c r="G5" t="n">
         <v>2.482206125847451e-25</v>
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02664330489333342</v>
+        <v>0.0266</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003269903538677247</v>
+        <v>0.0033</v>
       </c>
       <c r="D6" t="n">
-        <v>0.104789915597705</v>
+        <v>0.1048</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01286075121695442</v>
+        <v>0.0129</v>
       </c>
       <c r="F6" t="n">
-        <v>8.148040019587629</v>
+        <v>8.148</v>
       </c>
       <c r="G6" t="n">
         <v>3.698699617754467e-16</v>
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03331063289804159</v>
+        <v>0.0333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003469981940692815</v>
+        <v>0.0035</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1277329348017079</v>
+        <v>0.1277</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01330599086334616</v>
+        <v>0.0133</v>
       </c>
       <c r="F7" t="n">
-        <v>9.599655983048372</v>
+        <v>9.5997</v>
       </c>
       <c r="G7" t="n">
         <v>8.021169245052314e-22</v>
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03253244482086735</v>
+        <v>0.0325</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003312157832152412</v>
+        <v>0.0033</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1045299611148927</v>
+        <v>0.1045</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01064229052896763</v>
+        <v>0.0106</v>
       </c>
       <c r="F8" t="n">
-        <v>9.82213000390929</v>
+        <v>9.822100000000001</v>
       </c>
       <c r="G8" t="n">
         <v>9.041266072722864e-23</v>
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02017408230158348</v>
+        <v>0.0202</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00301505432183787</v>
+        <v>0.003</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0553096975563893</v>
+        <v>0.0553</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008266137718881407</v>
+        <v>0.0083</v>
       </c>
       <c r="F9" t="n">
-        <v>6.691117355818013</v>
+        <v>6.6911</v>
       </c>
       <c r="G9" t="n">
         <v>2.214729568316151e-11</v>
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04667305348598745</v>
+        <v>0.0467</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00469720135923217</v>
+        <v>0.0047</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1434937441943221</v>
+        <v>0.1435</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01444128806514111</v>
+        <v>0.0144</v>
       </c>
       <c r="F10" t="n">
-        <v>9.936353568120589</v>
+        <v>9.936400000000001</v>
       </c>
       <c r="G10" t="n">
         <v>2.892208930517625e-23</v>
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0212175155257281</v>
+        <v>0.0212</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00326493854102702</v>
+        <v>0.0033</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06528278255837758</v>
+        <v>0.0653</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01004567535637607</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>6.498595688436424</v>
+        <v>6.4986</v>
       </c>
       <c r="G11" t="n">
         <v>8.107322170513796e-11</v>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.02762940447276075</v>
+        <v>0.0276</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003235631339237121</v>
+        <v>0.0032</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07010716030727027</v>
+        <v>0.0701</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008210127193250297</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>8.539107696760984</v>
+        <v>8.539099999999999</v>
       </c>
       <c r="G12" t="n">
         <v>1.352622650770721e-17</v>
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02057661116401539</v>
+        <v>0.0206</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003456560515180043</v>
+        <v>0.0035</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0522113235874552</v>
+        <v>0.0522</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00877071535828489</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>5.952915065033545</v>
+        <v>5.9529</v>
       </c>
       <c r="G13" t="n">
         <v>2.63408016266086e-09</v>
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01711383370618993</v>
+        <v>0.0171</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003833596306944397</v>
+        <v>0.0038</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03616788187595865</v>
+        <v>0.0362</v>
       </c>
       <c r="E14" t="n">
-        <v>0.008101811713849166</v>
+        <v>0.0081</v>
       </c>
       <c r="F14" t="n">
-        <v>4.464172107842693</v>
+        <v>4.4642</v>
       </c>
       <c r="G14" t="n">
         <v>8.037893656124215e-06</v>
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.004852455773411404</v>
+        <v>0.0049</v>
       </c>
       <c r="C15" t="n">
-        <v>0.003026204169000148</v>
+        <v>0.003</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00953347009579103</v>
+        <v>0.0095</v>
       </c>
       <c r="E15" t="n">
-        <v>0.005945489932541639</v>
+        <v>0.0059</v>
       </c>
       <c r="F15" t="n">
-        <v>1.603479310192956</v>
+        <v>1.6035</v>
       </c>
       <c r="G15" t="n">
         <v>0.1088288734084694</v>
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01487801260484227</v>
+        <v>0.0149</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002894534065671969</v>
+        <v>0.0029</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03073597936671928</v>
+        <v>0.0307</v>
       </c>
       <c r="E16" t="n">
-        <v>0.005979719313438698</v>
+        <v>0.006</v>
       </c>
       <c r="F16" t="n">
-        <v>5.140037141483192</v>
+        <v>5.14</v>
       </c>
       <c r="G16" t="n">
         <v>2.746841668685638e-07</v>
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02977754030146236</v>
+        <v>0.0298</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007507123208594828</v>
+        <v>0.0075</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04323348094376889</v>
+        <v>0.0432</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01089945861530312</v>
+        <v>0.0109</v>
       </c>
       <c r="F17" t="n">
-        <v>3.966571411452307</v>
+        <v>3.9666</v>
       </c>
       <c r="G17" t="n">
         <v>7.291393614817315e-05</v>
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01645443665330604</v>
+        <v>0.0165</v>
       </c>
       <c r="C18" t="n">
-        <v>0.007074380159691944</v>
+        <v>0.0071</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01584433639750718</v>
+        <v>0.0158</v>
       </c>
       <c r="E18" t="n">
-        <v>0.006812075151262545</v>
+        <v>0.0068</v>
       </c>
       <c r="F18" t="n">
-        <v>2.325919201665091</v>
+        <v>2.3259</v>
       </c>
       <c r="G18" t="n">
         <v>0.02002286147083859</v>
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.00907438193967503</v>
+        <v>0.0091</v>
       </c>
       <c r="C19" t="n">
-        <v>0.007403063502005415</v>
+        <v>0.0074</v>
       </c>
       <c r="D19" t="n">
-        <v>0.006308837114027716</v>
+        <v>0.0063</v>
       </c>
       <c r="E19" t="n">
-        <v>0.005146876348101823</v>
+        <v>0.0051</v>
       </c>
       <c r="F19" t="n">
-        <v>1.225760381120177</v>
+        <v>1.2258</v>
       </c>
       <c r="G19" t="n">
         <v>0.2202888603984025</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.05994786740940758</v>
+        <v>-0.0599</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00211407167779509</v>
+        <v>0.0021</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2679187499639367</v>
+        <v>-0.2679</v>
       </c>
       <c r="E20" t="n">
-        <v>0.009448200006529977</v>
+        <v>0.0094</v>
       </c>
       <c r="F20" t="n">
-        <v>-28.35659170834326</v>
+        <v>-28.3566</v>
       </c>
       <c r="G20" t="n">
         <v>6.941543432780558e-177</v>
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05870536656163572</v>
+        <v>-0.0587</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00232773186094211</v>
+        <v>0.0023</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2236168427444969</v>
+        <v>-0.2236</v>
       </c>
       <c r="E21" t="n">
-        <v>0.008866651892091407</v>
+        <v>0.0089</v>
       </c>
       <c r="F21" t="n">
-        <v>-25.21998669463403</v>
+        <v>-25.22</v>
       </c>
       <c r="G21" t="n">
         <v>2.418274690132437e-140</v>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.07250601745455511</v>
+        <v>-0.0725</v>
       </c>
       <c r="C22" t="n">
-        <v>0.002746691218474138</v>
+        <v>0.0027</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1979657342389056</v>
+        <v>-0.198</v>
       </c>
       <c r="E22" t="n">
-        <v>0.007499387814723046</v>
+        <v>0.0075</v>
       </c>
       <c r="F22" t="n">
-        <v>-26.39758592698097</v>
+        <v>-26.3976</v>
       </c>
       <c r="G22" t="n">
         <v>1.460463677895199e-153</v>
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.04802488663967763</v>
+        <v>-0.048</v>
       </c>
       <c r="C23" t="n">
-        <v>0.002631729676753548</v>
+        <v>0.0026</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2042551850982722</v>
+        <v>-0.2043</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0111930390650792</v>
+        <v>0.0112</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.24841170576464</v>
+        <v>-18.2484</v>
       </c>
       <c r="G23" t="n">
         <v>2.130127519517401e-74</v>
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.03568878765466108</v>
+        <v>-0.0357</v>
       </c>
       <c r="C24" t="n">
-        <v>0.003754901798871801</v>
+        <v>0.0038</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.09209760362802473</v>
+        <v>-0.0921</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00968980680657801</v>
+        <v>0.0097</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.504586155990589</v>
+        <v>-9.5046</v>
       </c>
       <c r="G24" t="n">
         <v>2.008450123393033e-21</v>

--- a/output/coefficients/standardized/standardized_OTHER.xlsx
+++ b/output/coefficients/standardized/standardized_OTHER.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0988</v>
+        <v>0.105</v>
       </c>
       <c r="C2" t="n">
         <v>0.0035</v>
@@ -468,10 +468,10 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>28.4091</v>
+        <v>29.6153</v>
       </c>
       <c r="G2" t="n">
-        <v>1.56071571869917e-177</v>
+        <v>9.493174009798496e-193</v>
       </c>
     </row>
     <row r="3">
@@ -481,22 +481,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0259</v>
+        <v>0.025</v>
       </c>
       <c r="C3" t="n">
         <v>0.0016</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2115</v>
+        <v>0.2048</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0133</v>
+        <v>0.0132</v>
       </c>
       <c r="F3" t="n">
-        <v>15.9039</v>
+        <v>15.4752</v>
       </c>
       <c r="G3" t="n">
-        <v>5.952253279975866e-57</v>
+        <v>5.098290085572425e-54</v>
       </c>
     </row>
     <row r="4">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0537</v>
+        <v>-0.0502</v>
       </c>
       <c r="C4" t="n">
         <v>0.0024</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2596</v>
+        <v>-0.2425</v>
       </c>
       <c r="E4" t="n">
         <v>0.0117</v>
       </c>
       <c r="F4" t="n">
-        <v>-22.2787</v>
+        <v>-20.798</v>
       </c>
       <c r="G4" t="n">
-        <v>5.943237171671356e-110</v>
+        <v>4.516185900993735e-96</v>
       </c>
     </row>
     <row r="5">
@@ -531,22 +531,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0018</v>
+        <v>0.0017</v>
       </c>
       <c r="C5" t="n">
         <v>0.0002</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>0.008699999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>10.3999</v>
+        <v>10.1001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.482206125847451e-25</v>
+        <v>5.520102026723362e-24</v>
       </c>
     </row>
     <row r="6">
@@ -556,22 +556,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0266</v>
+        <v>0.0243</v>
       </c>
       <c r="C6" t="n">
         <v>0.0033</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1048</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0129</v>
+        <v>0.0128</v>
       </c>
       <c r="F6" t="n">
-        <v>8.148</v>
+        <v>7.4661</v>
       </c>
       <c r="G6" t="n">
-        <v>3.698699617754467e-16</v>
+        <v>8.263638734334532e-14</v>
       </c>
     </row>
     <row r="7">
@@ -581,22 +581,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0333</v>
+        <v>0.0286</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0035</v>
+        <v>0.0034</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1277</v>
+        <v>0.1095</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0133</v>
+        <v>0.0132</v>
       </c>
       <c r="F7" t="n">
-        <v>9.5997</v>
+        <v>8.3161</v>
       </c>
       <c r="G7" t="n">
-        <v>8.021169245052314e-22</v>
+        <v>9.090366403607607e-17</v>
       </c>
     </row>
     <row r="8">
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0325</v>
+        <v>0.0313</v>
       </c>
       <c r="C8" t="n">
         <v>0.0033</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1045</v>
+        <v>0.1006</v>
       </c>
       <c r="E8" t="n">
         <v>0.0106</v>
       </c>
       <c r="F8" t="n">
-        <v>9.822100000000001</v>
+        <v>9.5143</v>
       </c>
       <c r="G8" t="n">
-        <v>9.041266072722864e-23</v>
+        <v>1.828701716444621e-21</v>
       </c>
     </row>
     <row r="9">
@@ -631,22 +631,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0202</v>
+        <v>0.021</v>
       </c>
       <c r="C9" t="n">
         <v>0.003</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0553</v>
+        <v>0.0576</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0083</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>6.6911</v>
+        <v>6.9861</v>
       </c>
       <c r="G9" t="n">
-        <v>2.214729568316151e-11</v>
+        <v>2.826954633779415e-12</v>
       </c>
     </row>
     <row r="10">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0467</v>
+        <v>0.0449</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0047</v>
+        <v>0.0046</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1435</v>
+        <v>0.138</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0144</v>
+        <v>0.0142</v>
       </c>
       <c r="F10" t="n">
-        <v>9.936400000000001</v>
+        <v>9.6936</v>
       </c>
       <c r="G10" t="n">
-        <v>2.892208930517625e-23</v>
+        <v>3.210556741344724e-22</v>
       </c>
     </row>
     <row r="11">
@@ -681,22 +681,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0212</v>
+        <v>0.022</v>
       </c>
       <c r="C11" t="n">
         <v>0.0033</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0653</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>6.4986</v>
+        <v>6.7563</v>
       </c>
       <c r="G11" t="n">
-        <v>8.107322170513796e-11</v>
+        <v>1.415727937803293e-11</v>
       </c>
     </row>
     <row r="12">
@@ -706,22 +706,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0276</v>
+        <v>0.0254</v>
       </c>
       <c r="C12" t="n">
         <v>0.0032</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0701</v>
+        <v>0.0645</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0081</v>
       </c>
       <c r="F12" t="n">
-        <v>8.539099999999999</v>
+        <v>7.9973</v>
       </c>
       <c r="G12" t="n">
-        <v>1.352622650770721e-17</v>
+        <v>1.271356955724793e-15</v>
       </c>
     </row>
     <row r="13">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0206</v>
+        <v>0.0186</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0035</v>
+        <v>0.0034</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0522</v>
+        <v>0.0471</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.9529</v>
+        <v>5.3959</v>
       </c>
       <c r="G13" t="n">
-        <v>2.63408016266086e-09</v>
+        <v>6.818386801856259e-08</v>
       </c>
     </row>
     <row r="14">
@@ -756,22 +756,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0171</v>
+        <v>0.0174</v>
       </c>
       <c r="C14" t="n">
         <v>0.0038</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0081</v>
+        <v>0.008</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4642</v>
+        <v>4.6235</v>
       </c>
       <c r="G14" t="n">
-        <v>8.037893656124215e-06</v>
+        <v>3.774055178535852e-06</v>
       </c>
     </row>
     <row r="15">
@@ -781,22 +781,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0049</v>
+        <v>0.0037</v>
       </c>
       <c r="C15" t="n">
         <v>0.003</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0095</v>
+        <v>0.0073</v>
       </c>
       <c r="E15" t="n">
         <v>0.0059</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6035</v>
+        <v>1.2452</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1088288734084694</v>
+        <v>0.2130499859921222</v>
       </c>
     </row>
     <row r="16">
@@ -806,22 +806,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0149</v>
+        <v>0.0178</v>
       </c>
       <c r="C16" t="n">
         <v>0.0029</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0307</v>
+        <v>0.0368</v>
       </c>
       <c r="E16" t="n">
-        <v>0.006</v>
+        <v>0.0061</v>
       </c>
       <c r="F16" t="n">
-        <v>5.14</v>
+        <v>6.0578</v>
       </c>
       <c r="G16" t="n">
-        <v>2.746841668685638e-07</v>
+        <v>1.379790101527942e-09</v>
       </c>
     </row>
     <row r="17">
@@ -831,22 +831,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.0298</v>
+        <v>0.0253</v>
       </c>
       <c r="C17" t="n">
         <v>0.0075</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0432</v>
+        <v>0.0368</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0109</v>
+        <v>0.0108</v>
       </c>
       <c r="F17" t="n">
-        <v>3.9666</v>
+        <v>3.3951</v>
       </c>
       <c r="G17" t="n">
-        <v>7.291393614817315e-05</v>
+        <v>0.0006860189959474789</v>
       </c>
     </row>
     <row r="18">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0165</v>
+        <v>0.011</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0071</v>
+        <v>0.0069</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0158</v>
+        <v>0.0105</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0068</v>
+        <v>0.0067</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3259</v>
+        <v>1.5783</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02002286147083859</v>
+        <v>0.1145049998589514</v>
       </c>
     </row>
     <row r="19">
@@ -881,22 +881,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0091</v>
+        <v>0.0015</v>
       </c>
       <c r="C19" t="n">
         <v>0.0074</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0063</v>
+        <v>0.001</v>
       </c>
       <c r="E19" t="n">
         <v>0.0051</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2258</v>
+        <v>0.1989</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2202888603984025</v>
+        <v>0.8423610967934463</v>
       </c>
     </row>
     <row r="20">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0599</v>
+        <v>-0.0568</v>
       </c>
       <c r="C20" t="n">
         <v>0.0021</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2679</v>
+        <v>-0.2539</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0094</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-28.3566</v>
+        <v>-27.4281</v>
       </c>
       <c r="G20" t="n">
-        <v>6.941543432780558e-177</v>
+        <v>1.267181109150088e-165</v>
       </c>
     </row>
     <row r="21">
@@ -931,22 +931,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0587</v>
+        <v>-0.0563</v>
       </c>
       <c r="C21" t="n">
         <v>0.0023</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2236</v>
+        <v>-0.2144</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0089</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-25.22</v>
+        <v>-24.5696</v>
       </c>
       <c r="G21" t="n">
-        <v>2.418274690132437e-140</v>
+        <v>2.670911495138096e-133</v>
       </c>
     </row>
     <row r="22">
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.0725</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="C22" t="n">
         <v>0.0027</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.198</v>
+        <v>-0.195</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0075</v>
+        <v>0.0074</v>
       </c>
       <c r="F22" t="n">
-        <v>-26.3976</v>
+        <v>-26.2031</v>
       </c>
       <c r="G22" t="n">
-        <v>1.460463677895199e-153</v>
+        <v>2.452221048853129e-151</v>
       </c>
     </row>
     <row r="23">
@@ -981,22 +981,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.048</v>
+        <v>-0.0485</v>
       </c>
       <c r="C23" t="n">
         <v>0.0026</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2043</v>
+        <v>-0.2064</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0112</v>
+        <v>0.0111</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.2484</v>
+        <v>-18.5539</v>
       </c>
       <c r="G23" t="n">
-        <v>2.130127519517401e-74</v>
+        <v>7.578256781602136e-77</v>
       </c>
     </row>
     <row r="24">
@@ -1006,22 +1006,97 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0357</v>
+        <v>-0.0355</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0038</v>
+        <v>0.0037</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0921</v>
+        <v>-0.0917</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0097</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.5046</v>
+        <v>-9.533200000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>2.008450123393033e-21</v>
+        <v>1.525523201478916e-21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>d_aa</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.0769</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-12.6984</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.031610362271175e-37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>d_indie</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.0173</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.0573</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-9.868</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.728423285631834e-23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>d_unknown</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.0245</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.0863</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-15.8974</v>
+      </c>
+      <c r="G27" t="n">
+        <v>6.609746737921694e-57</v>
       </c>
     </row>
   </sheetData>
